--- a/output/topology_excel/6293.xlsx
+++ b/output/topology_excel/6293.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,81 +490,108 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>29068</v>
+      </c>
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1000</v>
+        <v>222726</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>341</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3926</v>
+        <v>232950</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>163</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>232950</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2119</v>
+        <v>18870</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>77</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -562,81 +604,108 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>353</v>
-      </c>
-      <c r="G5" t="n">
-        <v>20687</v>
+        <v>35432</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>71</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>35432</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1001</v>
+        <v>36445</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>66</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>35432</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>102</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1326</v>
+        <v>90445</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>72</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -649,110 +718,146 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>852</v>
+        <v>90445</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>79</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>222726</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>378</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7272</v>
+        <v>90445</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>79</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>792</v>
+        <v>93366</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>84</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>864</v>
+        <v>18032</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>90</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -765,23 +870,32 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>869</v>
+        <v>22701</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>77</v>
+      </c>
+      <c r="J12" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -794,81 +908,108 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>328</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7438</v>
+        <v>222726</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>241</v>
+      </c>
+      <c r="J13" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1264</v>
+        <v>232950</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>434</v>
+      </c>
+      <c r="J14" t="n">
+        <v>365</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>260</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4160</v>
+        <v>36445</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>197</v>
+      </c>
+      <c r="J15" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="16">
@@ -881,23 +1022,32 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1092</v>
+        <v>18870</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>102</v>
+      </c>
+      <c r="J16" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -910,23 +1060,32 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>105</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4390</v>
+        <v>35432</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>324</v>
+      </c>
+      <c r="J17" t="n">
+        <v>190</v>
       </c>
     </row>
     <row r="18">
@@ -939,23 +1098,32 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>990</v>
+        <v>90445</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>317</v>
+      </c>
+      <c r="J18" t="n">
+        <v>136</v>
       </c>
     </row>
     <row r="19">
@@ -968,23 +1136,32 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>273</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3003</v>
+        <v>93366</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>94</v>
+      </c>
+      <c r="J19" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -997,23 +1174,32 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>488149</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>847</v>
+        <v>18032</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>172</v>
+      </c>
+      <c r="J20" t="n">
+        <v>123</v>
       </c>
     </row>
     <row r="21">
@@ -1026,139 +1212,184 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>488149</v>
+      </c>
+      <c r="D21" t="n">
         <v>11</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F21" t="n">
+        <v>22701</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
         <v>141</v>
       </c>
-      <c r="G21" t="n">
-        <v>1551</v>
+      <c r="J21" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>232950</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>265</v>
-      </c>
-      <c r="G22" t="n">
-        <v>17392</v>
+        <v>18870</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>198</v>
+      </c>
+      <c r="J22" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>232950</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>197</v>
-      </c>
-      <c r="G23" t="n">
-        <v>9411</v>
+        <v>93366</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>351</v>
+      </c>
+      <c r="J23" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>29068</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>102</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1326</v>
+        <v>222726</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>182</v>
+      </c>
+      <c r="J24" t="n">
+        <v>182</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>222726</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>351</v>
-      </c>
-      <c r="G25" t="n">
-        <v>4563</v>
+        <v>35432</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>224</v>
+      </c>
+      <c r="J25" t="n">
+        <v>206</v>
       </c>
     </row>
     <row r="26">
@@ -1171,23 +1402,32 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>222726</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>21</v>
-      </c>
-      <c r="G26" t="n">
-        <v>4704</v>
+        <v>36445</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>185</v>
+      </c>
+      <c r="J26" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="27">
@@ -1200,81 +1440,222 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>222726</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>185</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2960</v>
+        <v>90445</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>260</v>
+      </c>
+      <c r="J27" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C28" t="n">
+        <v>35432</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>36445</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>185</v>
+      </c>
+      <c r="J28" t="n">
         <v>11</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>161</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2093</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>35432</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>90445</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>124</v>
+      </c>
+      <c r="J29" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>36445</v>
+      </c>
+      <c r="D30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>90445</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>197</v>
+      </c>
+      <c r="J30" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>93366</v>
+      </c>
+      <c r="D31" t="n">
+        <v>11</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>22701</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>161</v>
+      </c>
+      <c r="J31" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
         <v>10</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C32" t="n">
+        <v>18032</v>
+      </c>
+      <c r="D32" t="n">
         <v>11</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
+      <c r="F32" t="n">
+        <v>22701</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
         <v>161</v>
       </c>
-      <c r="G29" t="n">
-        <v>1771</v>
+      <c r="J32" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/6293.xlsx
+++ b/output/topology_excel/6293.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -971,7 +971,7 @@
         <v>434</v>
       </c>
       <c r="J14" t="n">
-        <v>365</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15">
@@ -1123,7 +1123,7 @@
         <v>317</v>
       </c>
       <c r="J18" t="n">
-        <v>136</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -1367,15 +1367,15 @@
         <v>222726</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>35432</v>
+        <v>36445</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="J25" t="n">
-        <v>206</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -1405,15 +1405,15 @@
         <v>222726</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>36445</v>
+        <v>90445</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="J26" t="n">
         <v>16</v>
@@ -1432,26 +1432,26 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>222726</v>
+        <v>35432</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>90445</v>
+        <v>36445</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1462,10 +1462,10 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>260</v>
+        <v>185</v>
       </c>
       <c r="J27" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -1481,15 +1481,15 @@
         <v>35432</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>36445</v>
+        <v>90445</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1500,23 +1500,23 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="J28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>35432</v>
+        <v>36445</v>
       </c>
       <c r="D29" t="n">
         <v>8</v>
@@ -1538,34 +1538,34 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>36445</v>
+        <v>93366</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>90445</v>
+        <v>22701</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1576,23 +1576,23 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="J30" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>93366</v>
+        <v>18032</v>
       </c>
       <c r="D31" t="n">
         <v>11</v>
@@ -1617,44 +1617,6 @@
         <v>161</v>
       </c>
       <c r="J31" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>10</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>18032</v>
-      </c>
-      <c r="D32" t="n">
-        <v>11</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>22701</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>161</v>
-      </c>
-      <c r="J32" t="n">
         <v>11</v>
       </c>
     </row>

--- a/output/topology_excel/6293.xlsx
+++ b/output/topology_excel/6293.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
         <v>12</v>
@@ -575,7 +575,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
@@ -597,7 +597,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,18 +608,18 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         <v>79</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,18 +652,18 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,18 +674,18 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
@@ -704,24 +704,24 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>241</v>
+        <v>77</v>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>434</v>
+        <v>197</v>
       </c>
       <c r="F14" t="n">
-        <v>167</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="F17" t="n">
-        <v>190</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>317</v>
+        <v>106</v>
       </c>
       <c r="F18" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>94</v>
+        <v>300</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>172</v>
+        <v>45</v>
       </c>
       <c r="F20" t="n">
-        <v>123</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="F21" t="n">
         <v>11</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>198</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>128</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>351</v>
+        <v>55</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -949,7 +949,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>182</v>
+        <v>237</v>
       </c>
       <c r="F24" t="n">
-        <v>182</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1004,18 +1004,18 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>260</v>
+        <v>334</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,15 +1048,15 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>124</v>
+        <v>351</v>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B29" t="n">
         <v>8</v>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>197</v>
+        <v>94</v>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1100,24 +1100,288 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" t="n">
+        <v>13</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>172</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>185</v>
+      </c>
+      <c r="F32" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>141</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>161</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" t="n">
+        <v>11</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>102</v>
+      </c>
+      <c r="F35" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>112</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
         <v>10</v>
       </c>
-      <c r="B31" t="n">
-        <v>11</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>161</v>
-      </c>
-      <c r="F31" t="n">
-        <v>11</v>
+      <c r="B37" t="n">
+        <v>12</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>182</v>
+      </c>
+      <c r="F37" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>12</v>
+      </c>
+      <c r="B38" t="n">
+        <v>13</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>241</v>
+      </c>
+      <c r="F38" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" t="n">
+        <v>14</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>185</v>
+      </c>
+      <c r="F39" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" t="n">
+        <v>14</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>197</v>
+      </c>
+      <c r="F40" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3</v>
+      </c>
+      <c r="B41" t="n">
+        <v>13</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>111</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>124</v>
+      </c>
+      <c r="F42" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>100</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/6293.xlsx
+++ b/output/topology_excel/6293.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
         </is>
       </c>
     </row>
@@ -481,6 +501,10 @@
       <c r="F2" t="n">
         <v>10</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -495,7 +519,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>163</v>
@@ -503,6 +527,10 @@
       <c r="F3" t="n">
         <v>26</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +553,10 @@
       <c r="F4" t="n">
         <v>13</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +579,10 @@
       <c r="F5" t="n">
         <v>18</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +605,10 @@
       <c r="F6" t="n">
         <v>12</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +631,10 @@
       <c r="F7" t="n">
         <v>12</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +657,10 @@
       <c r="F8" t="n">
         <v>12</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +683,10 @@
       <c r="F9" t="n">
         <v>11</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +709,10 @@
       <c r="F10" t="n">
         <v>16</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +735,10 @@
       <c r="F11" t="n">
         <v>13</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +761,10 @@
       <c r="F12" t="n">
         <v>11</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +787,10 @@
       <c r="F13" t="n">
         <v>11</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +813,10 @@
       <c r="F14" t="n">
         <v>22</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +839,10 @@
       <c r="F15" t="n">
         <v>16</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +865,10 @@
       <c r="F16" t="n">
         <v>12</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -803,13 +883,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>317</v>
+        <v>88</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>11</v>
+      </c>
+      <c r="G17" t="n">
+        <v>52</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>223</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -831,8 +923,12 @@
         <v>106</v>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +951,10 @@
       <c r="F19" t="n">
         <v>17</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +977,10 @@
       <c r="F20" t="n">
         <v>11</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +1003,10 @@
       <c r="F21" t="n">
         <v>11</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +1029,10 @@
       <c r="F22" t="n">
         <v>13</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1055,10 @@
       <c r="F23" t="n">
         <v>18</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1081,10 @@
       <c r="F24" t="n">
         <v>13</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1107,10 @@
       <c r="F25" t="n">
         <v>18</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1001,14 +1125,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>334</v>
+        <v>141</v>
       </c>
       <c r="F26" t="n">
-        <v>154</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G26" t="n">
+        <v>206</v>
+      </c>
+      <c r="H26" t="n">
+        <v>13</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1023,13 +1155,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F27" t="n">
-        <v>128</v>
+        <v>13</v>
+      </c>
+      <c r="G27" t="n">
+        <v>102</v>
+      </c>
+      <c r="H27" t="n">
+        <v>13</v>
+      </c>
+      <c r="I27" t="n">
+        <v>185</v>
+      </c>
+      <c r="J27" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -1053,6 +1197,10 @@
       <c r="F28" t="n">
         <v>13</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1223,10 @@
       <c r="F29" t="n">
         <v>13</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1249,10 @@
       <c r="F30" t="n">
         <v>13</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1275,10 @@
       <c r="F31" t="n">
         <v>12</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1301,10 @@
       <c r="F32" t="n">
         <v>11</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1327,10 @@
       <c r="F33" t="n">
         <v>11</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1353,10 @@
       <c r="F34" t="n">
         <v>11</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1379,10 @@
       <c r="F35" t="n">
         <v>13</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1405,10 @@
       <c r="F36" t="n">
         <v>11</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1243,14 +1423,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F37" t="n">
-        <v>182</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G37" t="n">
+        <v>169</v>
+      </c>
+      <c r="H37" t="n">
+        <v>10</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1461,10 @@
       <c r="F38" t="n">
         <v>16</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1487,10 @@
       <c r="F39" t="n">
         <v>16</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1315,8 +1511,12 @@
         <v>197</v>
       </c>
       <c r="F40" t="n">
-        <v>84</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1539,10 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1565,10 @@
       <c r="F42" t="n">
         <v>46</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1591,10 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
